--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_tips.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_tips.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -913,6 +918,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -925,9 +933,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1319,60 +1324,60 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="162" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1404,16 +1409,16 @@
       <c r="I3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1442,10 +1447,10 @@
       <c r="H4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K4" t="s">
@@ -1459,7 +1464,7 @@
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1494,10 +1499,10 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1526,10 +1531,10 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1558,10 +1563,10 @@
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1570,7 +1575,7 @@
       <c r="D8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1">
         <v>4001</v>
@@ -1595,15 +1600,15 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>49</v>
       </c>
       <c r="F9" s="1">
@@ -1632,15 +1637,15 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
       <c r="F10" s="1">
@@ -1669,16 +1674,16 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F11" s="1">
@@ -1707,7 +1712,7 @@
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1745,10 +1750,10 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1783,10 +1788,10 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1818,7 +1823,7 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="7">
+      <c r="A15" s="8">
         <v>11</v>
       </c>
       <c r="B15" t="s">
@@ -1847,7 +1852,7 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="7">
+      <c r="A16" s="8">
         <v>12</v>
       </c>
       <c r="B16" t="s">
@@ -1873,7 +1878,7 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <v>13</v>
       </c>
       <c r="B17" t="s">
